--- a/app/static/templates/script-batch-template.xlsx
+++ b/app/static/templates/script-batch-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批量任务" sheetId="1" r:id="R9ef5a8205758461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" r:id="Rb61ba1c28fc84234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批量任务" sheetId="1" r:id="Refe4b274b2674552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" r:id="R3063e40ab59248b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -90,7 +90,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -118,6 +118,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -321,16 +330,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>脚本编号</x:v>
+        <x:v>任务编号</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>脚本内容</x:v>
+        <x:v>口播脚本</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
@@ -350,7 +359,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -363,23 +372,23 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="13" t="str">
-        <x:v>脚本编号</x:v>
+      <x:c r="A2" s="16" t="str">
+        <x:v>任务编号</x:v>
       </x:c>
       <x:c r="B2" s="13" t="str">
         <x:v>每行必须唯一，用于历史记录和分段子任务归类。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
-        <x:v>脚本内容</x:v>
+      <x:c r="A3" s="17" t="str">
+        <x:v>口播脚本</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>填写一条完整口播脚本；系统只调用一次 MiniMax，再按约 30 秒、最长 45 秒切分音频。</x:v>
+        <x:v>每行填写一条完整口播脚本；系统只调用一次 MiniMax，再按约 30 秒、最长 45 秒切分音频。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="15" t="str">
+      <x:c r="A4" s="18" t="str">
         <x:v>素材顺序</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
